--- a/DesignerConfigs/Datas/Audio.xlsx
+++ b/DesignerConfigs/Datas/Audio.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -65,43 +65,97 @@
     <t>BGM</t>
   </si>
   <si>
-    <t>Audio/BGM.wav</t>
-  </si>
-  <si>
-    <t>点击音效</t>
-  </si>
-  <si>
-    <t>Audio/Click.wav</t>
-  </si>
-  <si>
-    <t>金钱奖励</t>
-  </si>
-  <si>
-    <t>Audio/CoinCollect.wav</t>
-  </si>
-  <si>
-    <t>箭头移出成功</t>
-  </si>
-  <si>
-    <t>Audio/EscapeArrow.wav</t>
-  </si>
-  <si>
-    <t>箭头移出成功失败</t>
-  </si>
-  <si>
-    <t>Audio/FailedArrow.wav</t>
-  </si>
-  <si>
-    <t>关卡成功</t>
-  </si>
-  <si>
-    <t>Audio/LevelCompetled.wav</t>
-  </si>
-  <si>
-    <t>关卡失败</t>
-  </si>
-  <si>
-    <t>Audio/LevelFailed.wav</t>
+    <t>Audio/bgm.ogg</t>
+  </si>
+  <si>
+    <t>按钮</t>
+  </si>
+  <si>
+    <t>Audio/button.wav</t>
+  </si>
+  <si>
+    <t>线框被点击</t>
+  </si>
+  <si>
+    <t>Audio/operate.wav</t>
+  </si>
+  <si>
+    <t>解锁线框</t>
+  </si>
+  <si>
+    <t>Audio/orderUnlock.wav</t>
+  </si>
+  <si>
+    <t>更换标靶</t>
+  </si>
+  <si>
+    <t>Audio/changeOrder.wav</t>
+  </si>
+  <si>
+    <t>更换标靶2</t>
+  </si>
+  <si>
+    <t>Audio/changeOrder2.wav</t>
+  </si>
+  <si>
+    <t>结算界面</t>
+  </si>
+  <si>
+    <t>Audio/gameWin.wav</t>
+  </si>
+  <si>
+    <t>点击2</t>
+  </si>
+  <si>
+    <t>Audio/click2.wav</t>
+  </si>
+  <si>
+    <t>线动画1</t>
+  </si>
+  <si>
+    <t>Audio/ropeTexture.wav</t>
+  </si>
+  <si>
+    <t>线动画2</t>
+  </si>
+  <si>
+    <t>Audio/ropeTexture2.wav</t>
+  </si>
+  <si>
+    <t>线动画3</t>
+  </si>
+  <si>
+    <t>Audio/ropeTexture3.wav</t>
+  </si>
+  <si>
+    <t>线动画4</t>
+  </si>
+  <si>
+    <t>Audio/ropeTexture4.wav</t>
+  </si>
+  <si>
+    <t>扫把音效</t>
+  </si>
+  <si>
+    <t>Audio/broom.wav</t>
+  </si>
+  <si>
+    <t>锤子音效</t>
+  </si>
+  <si>
+    <t>Audio/hammer.wav</t>
+  </si>
+  <si>
+    <t>胜利音效</t>
+  </si>
+  <si>
+    <t>Audio/levelComplete.wav</t>
+  </si>
+  <si>
+    <t>失败音效</t>
+  </si>
+  <si>
+    <t>Audio/levelFailed.wav</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="32.875" customWidth="1"/>
@@ -1142,7 +1196,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" customFormat="1" spans="1:6">
+    <row r="6" customFormat="1" spans="2:4">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1153,7 +1207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:6">
+    <row r="7" customFormat="1" spans="2:4">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1164,7 +1218,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="2:4">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1175,7 +1229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="2:4">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1186,7 +1240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="2:4">
       <c r="B10">
         <v>5</v>
       </c>
@@ -1197,7 +1251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="2:4">
       <c r="B11">
         <v>6</v>
       </c>
@@ -1208,7 +1262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="2:4">
       <c r="B12">
         <v>7</v>
       </c>
@@ -1217,6 +1271,105 @@
       </c>
       <c r="D12" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Audio.xlsx
+++ b/DesignerConfigs/Datas/Audio.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -68,94 +68,70 @@
     <t>Audio/bgm.ogg</t>
   </si>
   <si>
-    <t>按钮</t>
-  </si>
-  <si>
-    <t>Audio/button.wav</t>
-  </si>
-  <si>
-    <t>线框被点击</t>
-  </si>
-  <si>
-    <t>Audio/operate.wav</t>
-  </si>
-  <si>
-    <t>解锁线框</t>
-  </si>
-  <si>
-    <t>Audio/orderUnlock.wav</t>
-  </si>
-  <si>
-    <t>更换标靶</t>
-  </si>
-  <si>
-    <t>Audio/changeOrder.wav</t>
-  </si>
-  <si>
-    <t>更换标靶2</t>
-  </si>
-  <si>
-    <t>Audio/changeOrder2.wav</t>
-  </si>
-  <si>
-    <t>结算界面</t>
-  </si>
-  <si>
-    <t>Audio/gameWin.wav</t>
-  </si>
-  <si>
-    <t>点击2</t>
-  </si>
-  <si>
-    <t>Audio/click2.wav</t>
-  </si>
-  <si>
-    <t>线动画1</t>
-  </si>
-  <si>
-    <t>Audio/ropeTexture.wav</t>
-  </si>
-  <si>
-    <t>线动画2</t>
-  </si>
-  <si>
-    <t>Audio/ropeTexture2.wav</t>
-  </si>
-  <si>
-    <t>线动画3</t>
-  </si>
-  <si>
-    <t>Audio/ropeTexture3.wav</t>
-  </si>
-  <si>
-    <t>线动画4</t>
-  </si>
-  <si>
-    <t>Audio/ropeTexture4.wav</t>
-  </si>
-  <si>
-    <t>扫把音效</t>
-  </si>
-  <si>
-    <t>Audio/broom.wav</t>
-  </si>
-  <si>
-    <t>锤子音效</t>
-  </si>
-  <si>
-    <t>Audio/hammer.wav</t>
-  </si>
-  <si>
-    <t>胜利音效</t>
-  </si>
-  <si>
-    <t>Audio/levelComplete.wav</t>
-  </si>
-  <si>
-    <t>失败音效</t>
-  </si>
-  <si>
-    <t>Audio/levelFailed.wav</t>
+    <t>瓶子倒满</t>
+  </si>
+  <si>
+    <t>Audio/BottleCollected.mp3</t>
+  </si>
+  <si>
+    <t>瓶子移动</t>
+  </si>
+  <si>
+    <t>Audio/BottleMove.mp3</t>
+  </si>
+  <si>
+    <t>解锁瓶子</t>
+  </si>
+  <si>
+    <t>Audio/BottleUnlock.mp3</t>
+  </si>
+  <si>
+    <t>选中瓶子</t>
+  </si>
+  <si>
+    <t>Audio/BottleUp.mp3</t>
+  </si>
+  <si>
+    <t>按钮点击</t>
+  </si>
+  <si>
+    <t>Audio/ClickButton.mp3</t>
+  </si>
+  <si>
+    <t>打包成功</t>
+  </si>
+  <si>
+    <t>Audio/PackUp.mp3</t>
+  </si>
+  <si>
+    <t>倒水1</t>
+  </si>
+  <si>
+    <t>Audio/PourWater1.mp3</t>
+  </si>
+  <si>
+    <t>倒水2</t>
+  </si>
+  <si>
+    <t>Audio/PourWater2.mp3</t>
+  </si>
+  <si>
+    <t>倒水3</t>
+  </si>
+  <si>
+    <t>Audio/PourWater3.mp3</t>
+  </si>
+  <si>
+    <t>倒水4</t>
+  </si>
+  <si>
+    <t>Audio/PourWater4.mp3</t>
+  </si>
+  <si>
+    <t>关卡通过</t>
+  </si>
+  <si>
+    <t>Audio/Win.mp3</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="32.875" customWidth="1"/>
@@ -1196,7 +1172,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" customFormat="1" spans="2:4">
+    <row r="6" customFormat="1" spans="1:6">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1207,7 +1183,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="2:4">
+    <row r="7" customFormat="1" spans="1:6">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1218,7 +1194,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="1:6">
       <c r="B8">
         <v>3</v>
       </c>
@@ -1229,7 +1205,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="1:6">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1240,7 +1216,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="1:6">
       <c r="B10">
         <v>5</v>
       </c>
@@ -1251,7 +1227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="1:6">
       <c r="B11">
         <v>6</v>
       </c>
@@ -1262,7 +1238,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="1:6">
       <c r="B12">
         <v>7</v>
       </c>
@@ -1273,7 +1249,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="1:6">
       <c r="B13">
         <v>8</v>
       </c>
@@ -1284,7 +1260,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="1:6">
       <c r="B14">
         <v>9</v>
       </c>
@@ -1295,7 +1271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="1:6">
       <c r="B15">
         <v>10</v>
       </c>
@@ -1306,7 +1282,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="1:6">
       <c r="B16">
         <v>11</v>
       </c>
@@ -1326,50 +1302,6 @@
       </c>
       <c r="D17" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/Audio.xlsx
+++ b/DesignerConfigs/Datas/Audio.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -132,6 +132,18 @@
   </si>
   <si>
     <t>Audio/Win.mp3</t>
+  </si>
+  <si>
+    <t>获取奖励</t>
+  </si>
+  <si>
+    <t>Audio/reward.wav</t>
+  </si>
+  <si>
+    <t>飞钱音效</t>
+  </si>
+  <si>
+    <t>Audio/money.wav</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="32.875" customWidth="1"/>
@@ -1304,6 +1316,28 @@
         <v>34</v>
       </c>
     </row>
+    <row r="18" spans="2:4">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
